--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126385495</v>
       </c>
       <c r="B2" t="n">
-        <v>56963</v>
+        <v>56964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,117 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129725709</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92240</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skogen till norr, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561130</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6581384</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kung Karl</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>LarsErik Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>LarsErik Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31706-2025 artfynd.xlsx
+++ b/artfynd/A 31706-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129725709</v>
       </c>
       <c r="B3" t="n">
-        <v>92259</v>
+        <v>92276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
